--- a/AAII_Financials/Quarterly/PPCCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPCCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>PPCCY</t>
   </si>
@@ -656,78 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,8 +779,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -820,8 +832,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -867,8 +885,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -886,8 +910,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -933,8 +959,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -980,8 +1012,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1027,8 +1065,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1074,8 +1118,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1090,8 +1140,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1137,8 +1189,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1184,8 +1242,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,8 +1267,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,8 +1316,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1297,8 +1369,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1344,8 +1422,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1391,8 +1475,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1438,8 +1528,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1485,8 +1581,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1532,8 +1634,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1579,8 +1687,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1626,8 +1740,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1793,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1720,8 +1846,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1767,8 +1899,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1814,8 +1952,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1861,8 +2005,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1908,8 +2058,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1955,60 +2111,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2026,8 +2194,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2045,149 +2215,169 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1588300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1564200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1297900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1275100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1321400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1304500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1172300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1219900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1779900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1791300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1731800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1683000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1249400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1319100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1573500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1525500</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>26665900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>26261500</v>
+      </c>
+      <c r="F42" s="3">
         <v>23422300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>23011700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>18901000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>18659500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>17930800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>18658400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>17836800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>17951400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>20913100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>20323600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>21954700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>23179100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2688000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2606000</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>438700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>432000</v>
+      </c>
+      <c r="F43" s="3">
         <v>449400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>441500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>186100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>183700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>779300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>810900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>242900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>244400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>625400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>607800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>178800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>188800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>463100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>449000</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2233,243 +2423,279 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7149800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>7041300</v>
+      </c>
+      <c r="F45" s="3">
         <v>7720900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7585500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6523100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6439700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7399300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7699500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>6227600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>6267600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>7643200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>7427700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6242400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6590600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>7434200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>7207300</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36515900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>35962100</v>
+      </c>
+      <c r="F46" s="3">
         <v>33542800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>32954800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>27569400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27217300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>27916500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>29049100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>26739700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>26911600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>31580100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>30689800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>30272200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>31960500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12803900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12413200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>84970700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>83682100</v>
+      </c>
+      <c r="F47" s="3">
         <v>82138000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>80698100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>77173400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>76187600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>71805600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>74718900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>66807200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>67236500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>60178500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>58482000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>57223100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>60414500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>76639800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>74301100</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4236500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4172300</v>
+      </c>
+      <c r="F48" s="3">
         <v>4234700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4160400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3923500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3873400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4086100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4251900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3951100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3976500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4164100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4046700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4076100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4303400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>4397700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4263500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>358600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>353200</v>
+      </c>
+      <c r="F49" s="3">
         <v>421100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>413700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>316500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>312400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>370700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>385800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>317600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>319600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>396400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>385200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>318700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>336400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>400900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>388700</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2515,8 +2741,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2562,55 +2794,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1815500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1787900</v>
+      </c>
+      <c r="F52" s="3">
         <v>1332100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1308700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1658600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1637400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1293300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1345800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1756700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1768000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1480100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1438300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1569400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1657000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1503700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1457800</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2656,55 +2900,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>130264300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>128288800</v>
+      </c>
+      <c r="F54" s="3">
         <v>123026700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>120870000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>112315400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>110880600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>106621900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>110947900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>101369100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>102020500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>99229000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>96431600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>95541800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>100870300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>97497800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>94522600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2722,8 +2978,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2741,290 +2999,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>385800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>380000</v>
+      </c>
+      <c r="F57" s="3">
         <v>442900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>435200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>247200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>244100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>423800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>440900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>241800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>243300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>247800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>240800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>252400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>244700</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6095400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6003000</v>
+      </c>
+      <c r="F58" s="3">
         <v>9486200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9319900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4372400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4316500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5509900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5733400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5696700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5733300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5728800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5567300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4071100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>4298200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6120600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5933800</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3090000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3043200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1298000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1275300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1945500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1920600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>917400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>954600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2095800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2109300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>701000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>681300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2186600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2308600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1189000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14251900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>14035700</v>
+      </c>
+      <c r="F60" s="3">
         <v>15984100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15703900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10770100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10632500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>11189700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11643700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>11642700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11717500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10694100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10392600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9739100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10282300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11191600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>10850100</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1961300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1931600</v>
+      </c>
+      <c r="F61" s="3">
         <v>1805900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1774200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1867600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1843700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2898900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3016500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1295900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1304200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1282800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1246600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1328500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1402600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1313000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1272900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68950200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>67904600</v>
+      </c>
+      <c r="F62" s="3">
         <v>63960500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>62839200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>60444200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>59672000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>56827300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>59132900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>54643900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>54995100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>54209200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>52681000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>52682000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>55620200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>52863500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>51250300</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3070,8 +3366,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3117,8 +3419,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3164,55 +3472,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>85163400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>83871900</v>
+      </c>
+      <c r="F66" s="3">
         <v>81750400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>80317300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>73081900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>72148300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>70915900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>73793100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>67582500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>68016800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>66186100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>64320200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>63749700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>67305100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>65368100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>63373300</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3230,8 +3550,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3277,8 +3599,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3324,8 +3652,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3371,8 +3705,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3418,55 +3758,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37726000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>37153900</v>
+      </c>
+      <c r="F72" s="3">
         <v>33216600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>32634300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>30936500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>30541300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>27697900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>28821700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>26540300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>26710900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>26041700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>25307500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>24901600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>26290400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>24711800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>23957700</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3512,8 +3864,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3559,8 +3917,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3606,55 +3970,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44707300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44029300</v>
+      </c>
+      <c r="F76" s="3">
         <v>40886100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>40169400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>38851400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>38355100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>35336400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>36770100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>33416600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>33631300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>32636200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>31716100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>31392100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>33142900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>31710400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>30742700</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3700,60 +4076,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3799,8 +4187,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3818,55 +4212,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>89800</v>
+      </c>
+      <c r="F83" s="3">
         <v>95400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>99300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>89000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>89600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>100600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>97800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>94300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>99600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>107600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>104300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>113800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>120300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>116500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>114800</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3912,8 +4314,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3959,8 +4367,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4006,8 +4420,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4053,8 +4473,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4100,55 +4526,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2029900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1999100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1155000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1134700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1876900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1852900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1042500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1084800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1461800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1471200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>200300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>194600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1220400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1288500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1050100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1018000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4166,55 +4604,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-59900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-193900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-190500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-51000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-50300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-159800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-166300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-58400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-58800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-136500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-132700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-55000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-58100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-339200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-328800</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4260,8 +4706,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4307,55 +4759,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-418100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-411700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2249200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2209700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-813600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-803200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-756600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-787300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1135400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1142600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-314700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-305800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-459600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-485300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2420800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-2346900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4373,55 +4837,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F96" s="3">
         <v>909500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>893600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>1062000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1105100</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>749700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>728600</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>656300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>636300</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4467,8 +4939,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4514,8 +4992,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4561,145 +5045,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1833000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1805200</v>
+      </c>
+      <c r="F100" s="3">
         <v>1547300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1520200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1230700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1215000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-434100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-451700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>19700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>19900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-72600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-70500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-909600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-960400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1202600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1165900</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-5300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>8500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>8900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>8600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>14000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>14800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-224400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="F102" s="3">
         <v>450900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>443000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-167700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-165600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-148200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-154300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>346700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>348900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-192300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-186900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-140300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-148100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-159200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-154300</v>
       </c>
     </row>
